--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/171.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/171.xlsx
@@ -426,13 +426,13 @@
         <v>-4.909610350451016</v>
       </c>
       <c r="E2">
-        <v>-8.959510916825273</v>
+        <v>-8.811008668691739</v>
       </c>
       <c r="F2">
-        <v>-6.109700510907402</v>
+        <v>-6.120918295832938</v>
       </c>
       <c r="G2">
-        <v>-11.88229396385896</v>
+        <v>-14.23022555558519</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-4.818259338536169</v>
       </c>
       <c r="E3">
-        <v>-9.926054823600412</v>
+        <v>-10.5654345972174</v>
       </c>
       <c r="F3">
-        <v>-5.95951371968149</v>
+        <v>-5.738960499073731</v>
       </c>
       <c r="G3">
-        <v>-12.10184603347789</v>
+        <v>-12.75028258825493</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-4.825331173706768</v>
       </c>
       <c r="E4">
-        <v>-9.958610023241555</v>
+        <v>-11.41068785617109</v>
       </c>
       <c r="F4">
-        <v>-5.774261303928876</v>
+        <v>-6.046315849053769</v>
       </c>
       <c r="G4">
-        <v>-12.83910121452804</v>
+        <v>-13.07469949837581</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.927222401010559</v>
       </c>
       <c r="E5">
-        <v>-11.39257396014041</v>
+        <v>-11.40346946860287</v>
       </c>
       <c r="F5">
-        <v>-5.896992177551772</v>
+        <v>-6.269808427840584</v>
       </c>
       <c r="G5">
-        <v>-11.94057611807783</v>
+        <v>-13.66939100159556</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-5.0895881781919</v>
       </c>
       <c r="E6">
-        <v>-12.52147271703855</v>
+        <v>-12.21495842535537</v>
       </c>
       <c r="F6">
-        <v>-6.017505862893052</v>
+        <v>-5.817536859921216</v>
       </c>
       <c r="G6">
-        <v>-12.29756879630514</v>
+        <v>-12.6390714319542</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-5.281661254738821</v>
       </c>
       <c r="E7">
-        <v>-12.61942813829847</v>
+        <v>-12.06510216349354</v>
       </c>
       <c r="F7">
-        <v>-5.737078264593231</v>
+        <v>-4.888051939620228</v>
       </c>
       <c r="G7">
-        <v>-11.39174725748637</v>
+        <v>-13.6426666227298</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.465518081923243</v>
       </c>
       <c r="E8">
-        <v>-13.15928111017487</v>
+        <v>-13.3537745403303</v>
       </c>
       <c r="F8">
-        <v>-5.902535940108767</v>
+        <v>-5.478105130329869</v>
       </c>
       <c r="G8">
-        <v>-11.5680536707258</v>
+        <v>-13.52697298776889</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-5.604712600812183</v>
       </c>
       <c r="E9">
-        <v>-13.39351189974761</v>
+        <v>-13.77879899679421</v>
       </c>
       <c r="F9">
-        <v>-5.511728790620563</v>
+        <v>-5.290010754311999</v>
       </c>
       <c r="G9">
-        <v>-11.39703750925813</v>
+        <v>-13.6095164749723</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.674550062788491</v>
       </c>
       <c r="E10">
-        <v>-14.73459230627514</v>
+        <v>-14.82688260655146</v>
       </c>
       <c r="F10">
-        <v>-5.593986475868489</v>
+        <v>-5.288247297775157</v>
       </c>
       <c r="G10">
-        <v>-10.2741898470669</v>
+        <v>-13.58552660672198</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.668107561046259</v>
       </c>
       <c r="E11">
-        <v>-15.45882662584786</v>
+        <v>-15.98652970196168</v>
       </c>
       <c r="F11">
-        <v>-5.484699681761759</v>
+        <v>-5.500182782644052</v>
       </c>
       <c r="G11">
-        <v>-11.04188880489619</v>
+        <v>-12.78497048441542</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.589272207781808</v>
       </c>
       <c r="E12">
-        <v>-15.6210320363286</v>
+        <v>-16.79336791590831</v>
       </c>
       <c r="F12">
-        <v>-5.387811721267004</v>
+        <v>-5.55287030289185</v>
       </c>
       <c r="G12">
-        <v>-11.12186827457945</v>
+        <v>-12.15630119705336</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.450104127611646</v>
       </c>
       <c r="E13">
-        <v>-16.28067673112991</v>
+        <v>-16.33748643755613</v>
       </c>
       <c r="F13">
-        <v>-5.275289415975031</v>
+        <v>-5.328493224351262</v>
       </c>
       <c r="G13">
-        <v>-9.135180101552955</v>
+        <v>-11.76918917550976</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.276259733234186</v>
       </c>
       <c r="E14">
-        <v>-17.57463383713362</v>
+        <v>-17.90502677225924</v>
       </c>
       <c r="F14">
-        <v>-5.087953635090657</v>
+        <v>-5.770219686432675</v>
       </c>
       <c r="G14">
-        <v>-9.19988471411801</v>
+        <v>-11.1359844407589</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.1011202221768</v>
       </c>
       <c r="E15">
-        <v>-16.79264788854109</v>
+        <v>-18.25745526190619</v>
       </c>
       <c r="F15">
-        <v>-5.274339192425768</v>
+        <v>-5.471620646459102</v>
       </c>
       <c r="G15">
-        <v>-9.671409025821944</v>
+        <v>-11.28154912812065</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.963341756593301</v>
       </c>
       <c r="E16">
-        <v>-17.93557585791499</v>
+        <v>-17.83868462804687</v>
       </c>
       <c r="F16">
-        <v>-5.206868569310301</v>
+        <v>-4.980078714807541</v>
       </c>
       <c r="G16">
-        <v>-8.315128176565628</v>
+        <v>-9.377657699031333</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.906311004016229</v>
       </c>
       <c r="E17">
-        <v>-20.55009938319148</v>
+        <v>-20.04933167047528</v>
       </c>
       <c r="F17">
-        <v>-4.771458718272618</v>
+        <v>-5.036568712958308</v>
       </c>
       <c r="G17">
-        <v>-8.131502147138873</v>
+        <v>-10.29981346954086</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.960341658622919</v>
       </c>
       <c r="E18">
-        <v>-20.04188685920667</v>
+        <v>-20.85961605314175</v>
       </c>
       <c r="F18">
-        <v>-4.747600980509481</v>
+        <v>-4.814883934473968</v>
       </c>
       <c r="G18">
-        <v>-8.528628568938766</v>
+        <v>-9.81046849119903</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.13415476871556</v>
       </c>
       <c r="E19">
-        <v>-20.59605886589533</v>
+        <v>-21.28703607235571</v>
       </c>
       <c r="F19">
-        <v>-4.556617924901849</v>
+        <v>-4.756410344664112</v>
       </c>
       <c r="G19">
-        <v>-8.013633483758662</v>
+        <v>-9.023157861595095</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.423073056072408</v>
       </c>
       <c r="E20">
-        <v>-21.93896424744795</v>
+        <v>-20.67519847765338</v>
       </c>
       <c r="F20">
-        <v>-3.960273462443125</v>
+        <v>-4.361677188211535</v>
       </c>
       <c r="G20">
-        <v>-7.970278579376366</v>
+        <v>-9.276735718266652</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.803891443939071</v>
       </c>
       <c r="E21">
-        <v>-23.27434783367383</v>
+        <v>-22.79163967530022</v>
       </c>
       <c r="F21">
-        <v>-4.055436767195966</v>
+        <v>-4.309423603384568</v>
       </c>
       <c r="G21">
-        <v>-7.479030037349454</v>
+        <v>-9.590380113202743</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.23981011913804</v>
       </c>
       <c r="E22">
-        <v>-21.98209796237101</v>
+        <v>-23.13773282981044</v>
       </c>
       <c r="F22">
-        <v>-3.523171421634796</v>
+        <v>-4.233536375181497</v>
       </c>
       <c r="G22">
-        <v>-7.407207751874965</v>
+        <v>-9.405251096101159</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.694208721589701</v>
       </c>
       <c r="E23">
-        <v>-22.34084820173267</v>
+        <v>-23.95375931751862</v>
       </c>
       <c r="F23">
-        <v>-3.734161434072174</v>
+        <v>-3.901660506512711</v>
       </c>
       <c r="G23">
-        <v>-8.804804209461386</v>
+        <v>-8.919133899660117</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-7.134624476286189</v>
       </c>
       <c r="E24">
-        <v>-22.2644709591193</v>
+        <v>-22.97708521438833</v>
       </c>
       <c r="F24">
-        <v>-3.344770117672372</v>
+        <v>-3.713270769341612</v>
       </c>
       <c r="G24">
-        <v>-7.986592947793895</v>
+        <v>-10.05958042193811</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-7.531722457277626</v>
       </c>
       <c r="E25">
-        <v>-22.53032861116161</v>
+        <v>-23.55795710382621</v>
       </c>
       <c r="F25">
-        <v>-3.07323661179366</v>
+        <v>-3.63484565240905</v>
       </c>
       <c r="G25">
-        <v>-8.484111663072186</v>
+        <v>-10.25127756138961</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-7.866378724677195</v>
       </c>
       <c r="E26">
-        <v>-23.73031535303215</v>
+        <v>-22.69602547510227</v>
       </c>
       <c r="F26">
-        <v>-3.047559195933682</v>
+        <v>-3.703355186605045</v>
       </c>
       <c r="G26">
-        <v>-9.218893866604505</v>
+        <v>-11.21892022760872</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-8.135405523004021</v>
       </c>
       <c r="E27">
-        <v>-21.52414244292332</v>
+        <v>-22.29982475569718</v>
       </c>
       <c r="F27">
-        <v>-3.456542538213385</v>
+        <v>-3.194112173936618</v>
       </c>
       <c r="G27">
-        <v>-8.642190212572386</v>
+        <v>-10.32658916186249</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-8.339883350374212</v>
       </c>
       <c r="E28">
-        <v>-21.70050839162606</v>
+        <v>-22.78774065917962</v>
       </c>
       <c r="F28">
-        <v>-3.045829789074022</v>
+        <v>-3.464231430432843</v>
       </c>
       <c r="G28">
-        <v>-9.359750958209416</v>
+        <v>-10.27601395765904</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-8.484167009365132</v>
       </c>
       <c r="E29">
-        <v>-22.80411109271734</v>
+        <v>-22.3368540876579</v>
       </c>
       <c r="F29">
-        <v>-2.847268700661013</v>
+        <v>-3.289919255144085</v>
       </c>
       <c r="G29">
-        <v>-9.827299304720684</v>
+        <v>-11.22933520387527</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.579625041044116</v>
       </c>
       <c r="E30">
-        <v>-22.60578657355142</v>
+        <v>-22.42525895723564</v>
       </c>
       <c r="F30">
-        <v>-2.950657773938647</v>
+        <v>-3.565849128644058</v>
       </c>
       <c r="G30">
-        <v>-9.56509416637379</v>
+        <v>-11.06034509627763</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.632754016439351</v>
       </c>
       <c r="E31">
-        <v>-22.40632087893556</v>
+        <v>-22.2108628838165</v>
       </c>
       <c r="F31">
-        <v>-3.174636550441501</v>
+        <v>-3.373407479888306</v>
       </c>
       <c r="G31">
-        <v>-9.901965348813407</v>
+        <v>-10.77728021048779</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-8.643626358788639</v>
       </c>
       <c r="E32">
-        <v>-22.14299011538953</v>
+        <v>-21.1298663249715</v>
       </c>
       <c r="F32">
-        <v>-2.894791755918563</v>
+        <v>-3.321631382394844</v>
       </c>
       <c r="G32">
-        <v>-9.570447318510791</v>
+        <v>-10.84690760426974</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-8.614659514435958</v>
       </c>
       <c r="E33">
-        <v>-20.56531958433126</v>
+        <v>-22.05823066738797</v>
       </c>
       <c r="F33">
-        <v>-2.682482516453623</v>
+        <v>-3.477459334091551</v>
       </c>
       <c r="G33">
-        <v>-8.994505089952703</v>
+        <v>-10.14411851282894</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-8.546604851078367</v>
       </c>
       <c r="E34">
-        <v>-22.07405768404477</v>
+        <v>-21.63337829293635</v>
       </c>
       <c r="F34">
-        <v>-2.62990823117878</v>
+        <v>-3.003070521210115</v>
       </c>
       <c r="G34">
-        <v>-9.603711680089388</v>
+        <v>-10.67056477502938</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-8.436793593321434</v>
       </c>
       <c r="E35">
-        <v>-21.91049373136173</v>
+        <v>-20.45818041778379</v>
       </c>
       <c r="F35">
-        <v>-2.837208208833184</v>
+        <v>-2.9183161235865</v>
       </c>
       <c r="G35">
-        <v>-8.95854594430514</v>
+        <v>-10.62332329018398</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-8.283843084687277</v>
       </c>
       <c r="E36">
-        <v>-20.35599540180071</v>
+        <v>-20.38076615462267</v>
       </c>
       <c r="F36">
-        <v>-2.951202568773558</v>
+        <v>-2.666457788148249</v>
       </c>
       <c r="G36">
-        <v>-8.88881923415701</v>
+        <v>-10.17467815870195</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-8.091884173094805</v>
       </c>
       <c r="E37">
-        <v>-21.01234789599845</v>
+        <v>-19.13505993917068</v>
       </c>
       <c r="F37">
-        <v>-2.277721334144482</v>
+        <v>-2.746683578706665</v>
       </c>
       <c r="G37">
-        <v>-8.496880437217156</v>
+        <v>-10.39566700508492</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.863503232086585</v>
       </c>
       <c r="E38">
-        <v>-20.18651273358964</v>
+        <v>-19.69049086163347</v>
       </c>
       <c r="F38">
-        <v>-2.66302668928245</v>
+        <v>-3.008896183420059</v>
       </c>
       <c r="G38">
-        <v>-8.533965168348072</v>
+        <v>-9.94969348385308</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.60031121370898</v>
       </c>
       <c r="E39">
-        <v>-18.93186278197251</v>
+        <v>-18.69743273954343</v>
       </c>
       <c r="F39">
-        <v>-2.616370713013604</v>
+        <v>-2.448310216826042</v>
       </c>
       <c r="G39">
-        <v>-8.43785341025195</v>
+        <v>-9.026514754771917</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.312432876705599</v>
       </c>
       <c r="E40">
-        <v>-19.12118469481118</v>
+        <v>-18.56235741684263</v>
       </c>
       <c r="F40">
-        <v>-2.640984670351363</v>
+        <v>-2.770733736738529</v>
       </c>
       <c r="G40">
-        <v>-7.934163838088457</v>
+        <v>-10.20709171007695</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-7.008042160814809</v>
       </c>
       <c r="E41">
-        <v>-18.43954067328061</v>
+        <v>-18.45611488814868</v>
       </c>
       <c r="F41">
-        <v>-2.678909675908392</v>
+        <v>-2.375949901696656</v>
       </c>
       <c r="G41">
-        <v>-8.234635572323787</v>
+        <v>-10.1194913645623</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.692296886057609</v>
       </c>
       <c r="E42">
-        <v>-18.72379751521608</v>
+        <v>-19.313545213709</v>
       </c>
       <c r="F42">
-        <v>-2.820732916194868</v>
+        <v>-2.748268076475062</v>
       </c>
       <c r="G42">
-        <v>-7.869197692425799</v>
+        <v>-10.04344151243416</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.374612505139586</v>
       </c>
       <c r="E43">
-        <v>-18.10065232091659</v>
+        <v>-18.00577626198189</v>
       </c>
       <c r="F43">
-        <v>-2.383570694561751</v>
+        <v>-2.961058762538295</v>
       </c>
       <c r="G43">
-        <v>-7.374426729945102</v>
+        <v>-9.100184324657318</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.061548682359293</v>
       </c>
       <c r="E44">
-        <v>-17.19017092235642</v>
+        <v>-16.91007121955998</v>
       </c>
       <c r="F44">
-        <v>-2.881441906904366</v>
+        <v>-3.20880421371415</v>
       </c>
       <c r="G44">
-        <v>-7.769411228781087</v>
+        <v>-9.751524227872308</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.752702136117737</v>
       </c>
       <c r="E45">
-        <v>-17.10655264980478</v>
+        <v>-16.691047045705</v>
       </c>
       <c r="F45">
-        <v>-2.975995484879762</v>
+        <v>-2.546883240414824</v>
       </c>
       <c r="G45">
-        <v>-7.175426527033972</v>
+        <v>-10.16271053657749</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.446427862251773</v>
       </c>
       <c r="E46">
-        <v>-16.95201394581903</v>
+        <v>-16.83737109784084</v>
       </c>
       <c r="F46">
-        <v>-2.877385244201967</v>
+        <v>-2.823140941039293</v>
       </c>
       <c r="G46">
-        <v>-8.088710035498254</v>
+        <v>-10.35733750883124</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.141890803422261</v>
       </c>
       <c r="E47">
-        <v>-17.05008257892914</v>
+        <v>-15.27286936919688</v>
       </c>
       <c r="F47">
-        <v>-3.060885289359148</v>
+        <v>-3.137208828541921</v>
       </c>
       <c r="G47">
-        <v>-7.414229418963759</v>
+        <v>-9.024488700901882</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.835066922783851</v>
       </c>
       <c r="E48">
-        <v>-15.46169314989471</v>
+        <v>-15.50181542960267</v>
       </c>
       <c r="F48">
-        <v>-3.509622025675253</v>
+        <v>-3.071245893457952</v>
       </c>
       <c r="G48">
-        <v>-7.795465222175151</v>
+        <v>-9.775840184858254</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.522583402785576</v>
       </c>
       <c r="E49">
-        <v>-15.33687029234729</v>
+        <v>-17.18619492217768</v>
       </c>
       <c r="F49">
-        <v>-3.259615042452151</v>
+        <v>-3.388069429253445</v>
       </c>
       <c r="G49">
-        <v>-8.475577076671945</v>
+        <v>-11.25199257754604</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.210207829759841</v>
       </c>
       <c r="E50">
-        <v>-14.40019167165273</v>
+        <v>-14.50085964884324</v>
       </c>
       <c r="F50">
-        <v>-2.946164800256545</v>
+        <v>-3.406429331931134</v>
       </c>
       <c r="G50">
-        <v>-7.958519521620875</v>
+        <v>-9.66693316825285</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.905415284189089</v>
       </c>
       <c r="E51">
-        <v>-13.90942735801947</v>
+        <v>-15.87988866755505</v>
       </c>
       <c r="F51">
-        <v>-3.05648812988493</v>
+        <v>-3.802585448148735</v>
       </c>
       <c r="G51">
-        <v>-8.662225634176055</v>
+        <v>-9.2327187047765</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.617630148644773</v>
       </c>
       <c r="E52">
-        <v>-14.26518880453606</v>
+        <v>-15.22220933047307</v>
       </c>
       <c r="F52">
-        <v>-3.324558070926577</v>
+        <v>-3.618710064689596</v>
       </c>
       <c r="G52">
-        <v>-8.07273996381681</v>
+        <v>-10.62872941104961</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.364665501934852</v>
       </c>
       <c r="E53">
-        <v>-13.71139266119004</v>
+        <v>-13.9491194326967</v>
       </c>
       <c r="F53">
-        <v>-3.275078347010502</v>
+        <v>-3.851610648467078</v>
       </c>
       <c r="G53">
-        <v>-8.256025007053019</v>
+        <v>-10.12983681937252</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.161801049504109</v>
       </c>
       <c r="E54">
-        <v>-13.08955166740476</v>
+        <v>-12.57353658270473</v>
       </c>
       <c r="F54">
-        <v>-3.050557943084567</v>
+        <v>-3.540715715766034</v>
       </c>
       <c r="G54">
-        <v>-8.532786614136091</v>
+        <v>-10.24128633495209</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.019794075953238</v>
       </c>
       <c r="E55">
-        <v>-12.36322972131451</v>
+        <v>-12.85623562958157</v>
       </c>
       <c r="F55">
-        <v>-3.394961717397437</v>
+        <v>-3.190792726337857</v>
       </c>
       <c r="G55">
-        <v>-8.68781946174016</v>
+        <v>-10.26869434147171</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.952527766275003</v>
       </c>
       <c r="E56">
-        <v>-12.55696689631067</v>
+        <v>-12.35128813535629</v>
       </c>
       <c r="F56">
-        <v>-3.691672979919806</v>
+        <v>-3.931991642205208</v>
       </c>
       <c r="G56">
-        <v>-8.332968706476761</v>
+        <v>-10.73863290186234</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.969628415414383</v>
       </c>
       <c r="E57">
-        <v>-12.38473544437694</v>
+        <v>-12.20502748185655</v>
       </c>
       <c r="F57">
-        <v>-3.455853626140168</v>
+        <v>-3.775664031292179</v>
       </c>
       <c r="G57">
-        <v>-8.365991398230991</v>
+        <v>-9.219698329170548</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.072950332763574</v>
       </c>
       <c r="E58">
-        <v>-12.31640982854921</v>
+        <v>-11.58113056087179</v>
       </c>
       <c r="F58">
-        <v>-3.702431886056344</v>
+        <v>-3.818985514756068</v>
       </c>
       <c r="G58">
-        <v>-9.075825330579361</v>
+        <v>-10.70765943779691</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.262346691161941</v>
       </c>
       <c r="E59">
-        <v>-10.5644338044617</v>
+        <v>-11.27437626006621</v>
       </c>
       <c r="F59">
-        <v>-3.747062302459343</v>
+        <v>-3.61498598022944</v>
       </c>
       <c r="G59">
-        <v>-7.298572200003782</v>
+        <v>-10.14492297539498</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.53186205436963</v>
       </c>
       <c r="E60">
-        <v>-11.13972661392214</v>
+        <v>-11.12985906905942</v>
       </c>
       <c r="F60">
-        <v>-3.779493432195712</v>
+        <v>-4.362149924427293</v>
       </c>
       <c r="G60">
-        <v>-8.462248820330839</v>
+        <v>-10.0082835188071</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.866280171807788</v>
       </c>
       <c r="E61">
-        <v>-11.86286051431099</v>
+        <v>-12.38551434190626</v>
       </c>
       <c r="F61">
-        <v>-3.869567497989288</v>
+        <v>-4.078862945097146</v>
       </c>
       <c r="G61">
-        <v>-8.097228069170798</v>
+        <v>-9.845394746638341</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.245755040061612</v>
       </c>
       <c r="E62">
-        <v>-11.84700632681013</v>
+        <v>-11.19641858002416</v>
       </c>
       <c r="F62">
-        <v>-3.82495766976319</v>
+        <v>-3.930670831471731</v>
       </c>
       <c r="G62">
-        <v>-7.942072731381776</v>
+        <v>-11.70019409592581</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.649222310719527</v>
       </c>
       <c r="E63">
-        <v>-9.96633559989864</v>
+        <v>-11.52173056731318</v>
       </c>
       <c r="F63">
-        <v>-3.70920143699189</v>
+        <v>-3.886156025600559</v>
       </c>
       <c r="G63">
-        <v>-8.604704905431218</v>
+        <v>-11.19834518708215</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.050991672038606</v>
       </c>
       <c r="E64">
-        <v>-10.18146981458104</v>
+        <v>-10.78837137261501</v>
       </c>
       <c r="F64">
-        <v>-3.769596062077174</v>
+        <v>-3.673428687773944</v>
       </c>
       <c r="G64">
-        <v>-8.900512081001716</v>
+        <v>-9.799513896009582</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.426564649557669</v>
       </c>
       <c r="E65">
-        <v>-10.8024775691489</v>
+        <v>-10.77368100293413</v>
       </c>
       <c r="F65">
-        <v>-3.729997871220483</v>
+        <v>-4.036397454680553</v>
       </c>
       <c r="G65">
-        <v>-8.396398759009196</v>
+        <v>-10.44915879990846</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.759825517234817</v>
       </c>
       <c r="E66">
-        <v>-10.56052573139308</v>
+        <v>-11.48966897133887</v>
       </c>
       <c r="F66">
-        <v>-4.096788912354006</v>
+        <v>-4.20227481226368</v>
       </c>
       <c r="G66">
-        <v>-8.79647818743012</v>
+        <v>-11.14463489625301</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.03771275994774</v>
       </c>
       <c r="E67">
-        <v>-10.00934704602349</v>
+        <v>-11.90188690330909</v>
       </c>
       <c r="F67">
-        <v>-4.139273407241584</v>
+        <v>-4.124041323746887</v>
       </c>
       <c r="G67">
-        <v>-8.116217358384057</v>
+        <v>-11.36982813547086</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-6.250936367466199</v>
       </c>
       <c r="E68">
-        <v>-10.0394025280124</v>
+        <v>-11.52034485426683</v>
       </c>
       <c r="F68">
-        <v>-3.791368059149677</v>
+        <v>-3.915616123039563</v>
       </c>
       <c r="G68">
-        <v>-9.076474197505059</v>
+        <v>-10.83076538422025</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.400970156473617</v>
       </c>
       <c r="E69">
-        <v>-9.747945412404729</v>
+        <v>-10.73165223566894</v>
       </c>
       <c r="F69">
-        <v>-3.532372753003499</v>
+        <v>-3.807586791429693</v>
       </c>
       <c r="G69">
-        <v>-8.219585832302261</v>
+        <v>-10.71392630050276</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.492038400574204</v>
       </c>
       <c r="E70">
-        <v>-9.706364964066299</v>
+        <v>-11.03330747474188</v>
       </c>
       <c r="F70">
-        <v>-3.661472499965334</v>
+        <v>-4.273607302253946</v>
       </c>
       <c r="G70">
-        <v>-8.036022703240752</v>
+        <v>-10.2325200103641</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.529506106152096</v>
       </c>
       <c r="E71">
-        <v>-10.06069994127047</v>
+        <v>-11.0180872736021</v>
       </c>
       <c r="F71">
-        <v>-3.688514278471462</v>
+        <v>-4.120438392789262</v>
       </c>
       <c r="G71">
-        <v>-9.169838202803584</v>
+        <v>-10.32800938589883</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.524489856420998</v>
       </c>
       <c r="E72">
-        <v>-10.02775982133868</v>
+        <v>-11.56672548505339</v>
       </c>
       <c r="F72">
-        <v>-3.808134753676435</v>
+        <v>-3.86675404443051</v>
       </c>
       <c r="G72">
-        <v>-8.964412231000729</v>
+        <v>-11.10526919924554</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.488715649288169</v>
       </c>
       <c r="E73">
-        <v>-10.94141568017824</v>
+        <v>-10.91504184755756</v>
       </c>
       <c r="F73">
-        <v>-3.87473750595024</v>
+        <v>-4.062980750324162</v>
       </c>
       <c r="G73">
-        <v>-9.140400831868385</v>
+        <v>-10.50221360272082</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.430907245947296</v>
       </c>
       <c r="E74">
-        <v>-10.82265192085307</v>
+        <v>-11.20788920468559</v>
       </c>
       <c r="F74">
-        <v>-4.08630002807605</v>
+        <v>-4.001631942424826</v>
       </c>
       <c r="G74">
-        <v>-9.027656892982966</v>
+        <v>-11.11244315142914</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.360424653665302</v>
       </c>
       <c r="E75">
-        <v>-11.16525815037738</v>
+        <v>-12.66281997623996</v>
       </c>
       <c r="F75">
-        <v>-3.916867250712761</v>
+        <v>-4.512436489125877</v>
       </c>
       <c r="G75">
-        <v>-8.386182415475005</v>
+        <v>-10.51145664586647</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.289630596085788</v>
       </c>
       <c r="E76">
-        <v>-11.5783636632531</v>
+        <v>-10.83574826768326</v>
       </c>
       <c r="F76">
-        <v>-4.189457088437072</v>
+        <v>-4.306966483656764</v>
       </c>
       <c r="G76">
-        <v>-9.242736415578335</v>
+        <v>-10.72390428475812</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.225026372451587</v>
       </c>
       <c r="E77">
-        <v>-11.40648090381797</v>
+        <v>-14.31111205944785</v>
       </c>
       <c r="F77">
-        <v>-4.305396239241605</v>
+        <v>-4.133334510058686</v>
       </c>
       <c r="G77">
-        <v>-8.878993534996454</v>
+        <v>-11.25430664887799</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.167927428748842</v>
       </c>
       <c r="E78">
-        <v>-12.60211578216714</v>
+        <v>-12.93130867168073</v>
       </c>
       <c r="F78">
-        <v>-4.250686326539792</v>
+        <v>-4.24514098027688</v>
       </c>
       <c r="G78">
-        <v>-9.432096309879109</v>
+        <v>-11.75698981519755</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.121716468411304</v>
       </c>
       <c r="E79">
-        <v>-12.64720126938751</v>
+        <v>-13.99169614531682</v>
       </c>
       <c r="F79">
-        <v>-4.299078836344917</v>
+        <v>-4.180764126667224</v>
       </c>
       <c r="G79">
-        <v>-8.763207204760445</v>
+        <v>-10.48295946986442</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-6.083790918768347</v>
       </c>
       <c r="E80">
-        <v>-12.9835400908852</v>
+        <v>-13.74838123688469</v>
       </c>
       <c r="F80">
-        <v>-4.697469561609203</v>
+        <v>-4.136124208028733</v>
       </c>
       <c r="G80">
-        <v>-9.024733681271789</v>
+        <v>-11.08845824899712</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.044898721554158</v>
       </c>
       <c r="E81">
-        <v>-13.44839700472058</v>
+        <v>-14.77059367463612</v>
       </c>
       <c r="F81">
-        <v>-4.551049614903164</v>
+        <v>-4.759419385903447</v>
       </c>
       <c r="G81">
-        <v>-9.501717082569982</v>
+        <v>-10.5109368902168</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-5.999598397499131</v>
       </c>
       <c r="E82">
-        <v>-14.05518535090436</v>
+        <v>-14.87240282727657</v>
       </c>
       <c r="F82">
-        <v>-4.570109515595478</v>
+        <v>-4.504027802567851</v>
       </c>
       <c r="G82">
-        <v>-9.196640379489525</v>
+        <v>-9.925430495595762</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-5.942583167066952</v>
       </c>
       <c r="E83">
-        <v>-15.64596581421483</v>
+        <v>-16.55975752727462</v>
       </c>
       <c r="F83">
-        <v>-4.641472887851094</v>
+        <v>-4.88956517062243</v>
       </c>
       <c r="G83">
-        <v>-9.173592361445118</v>
+        <v>-10.80747569635148</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.866887012545559</v>
       </c>
       <c r="E84">
-        <v>-15.51916401352605</v>
+        <v>-16.64391468823316</v>
       </c>
       <c r="F84">
-        <v>-4.96967851806085</v>
+        <v>-4.701442287898082</v>
       </c>
       <c r="G84">
-        <v>-9.032596226927557</v>
+        <v>-11.09660219102373</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.7694297156206</v>
       </c>
       <c r="E85">
-        <v>-15.38764354292129</v>
+        <v>-16.93657637792688</v>
       </c>
       <c r="F85">
-        <v>-4.890647633615633</v>
+        <v>-4.930994917370326</v>
       </c>
       <c r="G85">
-        <v>-8.869118177652808</v>
+        <v>-10.44419960269063</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.65200881730184</v>
       </c>
       <c r="E86">
-        <v>-18.75220916114021</v>
+        <v>-19.47349544413393</v>
       </c>
       <c r="F86">
-        <v>-5.20554221560612</v>
+        <v>-4.962249353611524</v>
       </c>
       <c r="G86">
-        <v>-8.524139469187514</v>
+        <v>-11.67037270170805</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.515765842453791</v>
       </c>
       <c r="E87">
-        <v>-19.75558314701973</v>
+        <v>-18.91301527315258</v>
       </c>
       <c r="F87">
-        <v>-5.132792308821537</v>
+        <v>-5.453343096489015</v>
       </c>
       <c r="G87">
-        <v>-9.15305373691948</v>
+        <v>-11.46837314453834</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-5.361899041112937</v>
       </c>
       <c r="E88">
-        <v>-20.20025665220292</v>
+        <v>-21.00031121208606</v>
       </c>
       <c r="F88">
-        <v>-5.363708509086973</v>
+        <v>-4.869174956961148</v>
       </c>
       <c r="G88">
-        <v>-9.066986173989507</v>
+        <v>-9.746584893927714</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-5.198071318917956</v>
       </c>
       <c r="E89">
-        <v>-20.81426338595493</v>
+        <v>-22.74452543172442</v>
       </c>
       <c r="F89">
-        <v>-5.326108955095568</v>
+        <v>-5.473900391124377</v>
       </c>
       <c r="G89">
-        <v>-9.523881184955401</v>
+        <v>-10.93567657235976</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.030869182729941</v>
       </c>
       <c r="E90">
-        <v>-22.32721296649557</v>
+        <v>-24.63681622293959</v>
       </c>
       <c r="F90">
-        <v>-5.357475834456761</v>
+        <v>-5.566872638743208</v>
       </c>
       <c r="G90">
-        <v>-8.86501641172965</v>
+        <v>-10.46367885264371</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.867705552628068</v>
       </c>
       <c r="E91">
-        <v>-24.32771164412403</v>
+        <v>-24.87538981908569</v>
       </c>
       <c r="F91">
-        <v>-5.621192959789822</v>
+        <v>-5.302101557123422</v>
       </c>
       <c r="G91">
-        <v>-9.274176666564795</v>
+        <v>-11.30868566990606</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.72538589328095</v>
       </c>
       <c r="E92">
-        <v>-25.57173326724516</v>
+        <v>-25.96426139423003</v>
       </c>
       <c r="F92">
-        <v>-5.164468802689198</v>
+        <v>-5.543925531881448</v>
       </c>
       <c r="G92">
-        <v>-9.264602568865222</v>
+        <v>-11.77786611536819</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.620253967224478</v>
       </c>
       <c r="E93">
-        <v>-28.53273486732252</v>
+        <v>-28.98556415419353</v>
       </c>
       <c r="F93">
-        <v>-5.340036064915942</v>
+        <v>-5.185226436122863</v>
       </c>
       <c r="G93">
-        <v>-9.790009319766334</v>
+        <v>-9.942019639293049</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.566325077973946</v>
       </c>
       <c r="E94">
-        <v>-30.02806415549932</v>
+        <v>-30.65192711292902</v>
       </c>
       <c r="F94">
-        <v>-5.193651751593001</v>
+        <v>-4.659004512335009</v>
       </c>
       <c r="G94">
-        <v>-9.627689961430329</v>
+        <v>-11.09878052998857</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.583356091533866</v>
       </c>
       <c r="E95">
-        <v>-31.83799558993699</v>
+        <v>-33.14339162128408</v>
       </c>
       <c r="F95">
-        <v>-5.411412106818883</v>
+        <v>-5.36956109429748</v>
       </c>
       <c r="G95">
-        <v>-10.22518053090353</v>
+        <v>-10.98006105640477</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.700680523783396</v>
       </c>
       <c r="E96">
-        <v>-34.65670121550833</v>
+        <v>-34.37363762647388</v>
       </c>
       <c r="F96">
-        <v>-5.1990624828531</v>
+        <v>-4.835667699055238</v>
       </c>
       <c r="G96">
-        <v>-10.33610366974235</v>
+        <v>-11.16182986978399</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.923793849838341</v>
       </c>
       <c r="E97">
-        <v>-37.43377657952716</v>
+        <v>-38.37594597495602</v>
       </c>
       <c r="F97">
-        <v>-5.277692689701711</v>
+        <v>-4.873973585884929</v>
       </c>
       <c r="G97">
-        <v>-10.12349050357374</v>
+        <v>-12.05315121914075</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.293150648124477</v>
       </c>
       <c r="E98">
-        <v>-39.14263700258764</v>
+        <v>-39.71325189839815</v>
       </c>
       <c r="F98">
-        <v>-5.142786285000917</v>
+        <v>-5.171991405787535</v>
       </c>
       <c r="G98">
-        <v>-10.4968505189472</v>
+        <v>-11.84661952512777</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.787650117542408</v>
       </c>
       <c r="E99">
-        <v>-41.89973047504763</v>
+        <v>-43.88669807234116</v>
       </c>
       <c r="F99">
-        <v>-4.96184788416196</v>
+        <v>-4.977405419222279</v>
       </c>
       <c r="G99">
-        <v>-11.24230923184367</v>
+        <v>-11.90723892449737</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-6.45949784703665</v>
       </c>
       <c r="E100">
-        <v>-45.01847241023417</v>
+        <v>-45.58680042667081</v>
       </c>
       <c r="F100">
-        <v>-5.201111006454721</v>
+        <v>-4.506762070830858</v>
       </c>
       <c r="G100">
-        <v>-11.58236184854653</v>
+        <v>-12.74662443543404</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.208410166517365</v>
       </c>
       <c r="E101">
-        <v>-47.39482084507724</v>
+        <v>-47.58140755961529</v>
       </c>
       <c r="F101">
-        <v>-5.197793934414833</v>
+        <v>-4.63538670601806</v>
       </c>
       <c r="G101">
-        <v>-12.5949915180988</v>
+        <v>-13.40327114314848</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.158955108032988</v>
       </c>
       <c r="E102">
-        <v>-50.01200937730725</v>
+        <v>-49.73764385472303</v>
       </c>
       <c r="F102">
-        <v>-4.583727010909384</v>
+        <v>-4.239255137242149</v>
       </c>
       <c r="G102">
-        <v>-12.46873062177654</v>
+        <v>-13.61617232677901</v>
       </c>
     </row>
   </sheetData>
